--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.3047329008612</v>
+        <v>6.874519096389946</v>
       </c>
       <c r="D2" t="n">
-        <v>42.11369915428167</v>
+        <v>6.843476112570771</v>
       </c>
       <c r="E2" t="n">
-        <v>14.03759906636495</v>
+        <v>2.281109848284305</v>
       </c>
       <c r="F2" t="n">
-        <v>14.06861947022178</v>
+        <v>2.286150663911039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.37993103359111</v>
+        <v>11.43673879295856</v>
       </c>
       <c r="D3" t="n">
-        <v>70.25093809472523</v>
+        <v>11.41577744039285</v>
       </c>
       <c r="E3" t="n">
-        <v>14.03759906636495</v>
+        <v>2.281109848284305</v>
       </c>
       <c r="F3" t="n">
-        <v>14.06861947022178</v>
+        <v>2.286150663911039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
